--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2073,15 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89594505</v>
+        <v>127456613</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,34 +2084,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463521.9401843805</v>
+        <v>463188</v>
       </c>
       <c r="R14" t="n">
-        <v>7055844.888383466</v>
+        <v>7054869</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,22 +2138,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,55 +2157,45 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89594508</v>
+        <v>127456602</v>
       </c>
       <c r="B15" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2226,14 +2206,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463507.9449135439</v>
+        <v>463073</v>
       </c>
       <c r="R15" t="n">
-        <v>7055828.152650622</v>
+        <v>7055011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,22 +2240,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,75 +2261,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89594529</v>
+        <v>127456612</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463422.1366394605</v>
+        <v>463233</v>
       </c>
       <c r="R16" t="n">
-        <v>7055838.924257813</v>
+        <v>7054875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,22 +2342,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,28 +2363,3320 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127456611</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>463253</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7054891</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127456637</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>463218</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7054785</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127456609</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>463323</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7055206</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127456631</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>463258</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7054968</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127456630</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>463334</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7055224</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127456614</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>463186</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7054865</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127456610</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>463220</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7054981</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127456639</v>
+      </c>
+      <c r="B24" t="n">
+        <v>88729</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>510</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>463369</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7055407</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127456600</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>463051</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7054759</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127456604</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>463298</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7055633</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127456601</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>463062</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7054993</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127456638</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88729</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>510</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>463269</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7055595</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127456625</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>463207</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7055365</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127456640</v>
+      </c>
+      <c r="B30" t="n">
+        <v>88729</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>510</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>463328</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7055209</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127456636</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>463274</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7055044</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>89594505</v>
+      </c>
+      <c r="B32" t="n">
+        <v>81236</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>463521.9401843805</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7055844.888383466</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>89594508</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5135</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>463507.9449135439</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7055828.152650622</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>89594529</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5113</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>463422.1366394605</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7055838.924257813</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127456608</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>463435</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7055686</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127456628</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>463461</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7055899</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127456629</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>463485</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7055874</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127456633</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>463600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7056150</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127456623</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>463387</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7055632</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127456632</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>463475</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7056315</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127456605</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>463648</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7056396</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127456606</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>463477</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7055687</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127456624</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57490</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>463434</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7056142</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127456635</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463389</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7055462</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127456607</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>463448</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7055699</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127456626</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57761</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>463436</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7056149</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127456634</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>463385</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7055637</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127456627</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>463538</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7055899</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -5164,10 +5164,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R44" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,10 +5266,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5277,21 +5277,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R45" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>127456613</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127456602</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127456612</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127456611</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127456637</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127456609</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127456631</v>
       </c>
       <c r="B20" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127456614</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127456610</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127456600</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>127456604</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127456601</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127456625</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127456636</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127456608</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>127456628</v>
       </c>
       <c r="B36" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>127456629</v>
       </c>
       <c r="B37" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>127456633</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>127456623</v>
       </c>
       <c r="B39" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>127456632</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>127456605</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>127456606</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>127456624</v>
       </c>
       <c r="B43" t="n">
-        <v>57490</v>
+        <v>57494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>127456607</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>127456635</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5368,61 +5368,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B46" t="n">
-        <v>57761</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R46" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,6 +5439,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5481,45 +5470,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57765</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R47" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,11 +5557,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5586,7 +5586,7 @@
         <v>127456627</v>
       </c>
       <c r="B48" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R19" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,11 +2654,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,21 +2691,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R20" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,6 +2751,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B41" t="n">
         <v>57661</v>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R41" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,7 +4953,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B42" t="n">
         <v>57661</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R42" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5164,10 +5164,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R44" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,10 +5266,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5277,21 +5277,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R45" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,45 +5368,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>57765</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R46" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5439,11 +5455,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5470,61 +5481,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B47" t="n">
-        <v>57765</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R47" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5557,6 +5552,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R19" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,6 +2654,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,21 +2696,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R20" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,11 +2756,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3879,15 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89594505</v>
+        <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3895,34 +3890,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463521.9401843805</v>
+        <v>463244</v>
       </c>
       <c r="R32" t="n">
-        <v>7055844.888383466</v>
+        <v>7055263</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,22 +3944,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,55 +3958,45 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89594508</v>
+        <v>127690748</v>
       </c>
       <c r="B33" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4032,14 +4007,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463507.9449135439</v>
+        <v>463192</v>
       </c>
       <c r="R33" t="n">
-        <v>7055828.152650622</v>
+        <v>7055213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,22 +4041,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4092,75 +4062,61 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89594529</v>
+        <v>127690750</v>
       </c>
       <c r="B34" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463422.1366394605</v>
+        <v>463270</v>
       </c>
       <c r="R34" t="n">
-        <v>7055838.924257813</v>
+        <v>7055207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4187,22 +4143,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,32 +4164,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127456608</v>
+        <v>127690754</v>
       </c>
       <c r="B35" t="n">
         <v>57661</v>
@@ -4273,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463435</v>
+        <v>463174</v>
       </c>
       <c r="R35" t="n">
-        <v>7055686</v>
+        <v>7054944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4303,12 +4245,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4340,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127456628</v>
+        <v>127690753</v>
       </c>
       <c r="B36" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4351,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4317,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463461</v>
+        <v>463141</v>
       </c>
       <c r="R36" t="n">
-        <v>7055899</v>
+        <v>7054981</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,12 +4347,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4437,7 +4384,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127456629</v>
+        <v>127690768</v>
       </c>
       <c r="B37" t="n">
         <v>91348</v>
@@ -4472,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463485</v>
+        <v>463242</v>
       </c>
       <c r="R37" t="n">
-        <v>7055874</v>
+        <v>7055254</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,12 +4449,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127456633</v>
+        <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>91326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4545,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4569,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463600</v>
+        <v>463254</v>
       </c>
       <c r="R38" t="n">
-        <v>7056150</v>
+        <v>7055069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,17 +4546,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127456623</v>
+        <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,50 +4589,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463387</v>
+        <v>463101</v>
       </c>
       <c r="R39" t="n">
-        <v>7055632</v>
+        <v>7054992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,12 +4643,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4749,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127456632</v>
+        <v>127690749</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4760,21 +4691,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4784,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463475</v>
+        <v>463268</v>
       </c>
       <c r="R40" t="n">
-        <v>7056315</v>
+        <v>7055199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4814,17 +4745,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127456606</v>
+        <v>127690763</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57572</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4862,16 +4793,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100011</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4879,17 +4810,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463477</v>
+        <v>463125</v>
       </c>
       <c r="R41" t="n">
-        <v>7055687</v>
+        <v>7054733</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,17 +4863,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127456605</v>
+        <v>127690743</v>
       </c>
       <c r="B42" t="n">
         <v>57661</v>
@@ -4988,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463648</v>
+        <v>463122</v>
       </c>
       <c r="R42" t="n">
-        <v>7056396</v>
+        <v>7054927</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,17 +4960,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5055,27 +4997,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127456624</v>
+        <v>127690756</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102622</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5083,29 +5025,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463434</v>
+        <v>463174</v>
       </c>
       <c r="R43" t="n">
-        <v>7056142</v>
+        <v>7054942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5132,12 +5062,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5164,10 +5099,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127456635</v>
+        <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>91326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5175,21 +5110,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5134,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463389</v>
+        <v>463238</v>
       </c>
       <c r="R44" t="n">
-        <v>7055462</v>
+        <v>7055089</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,17 +5164,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,7 +5196,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127456607</v>
+        <v>127690751</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5301,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463448</v>
+        <v>463252</v>
       </c>
       <c r="R45" t="n">
-        <v>7055699</v>
+        <v>7055162</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,17 +5261,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,61 +5298,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127456626</v>
+        <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>57765</v>
+        <v>91326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463436</v>
+        <v>463175</v>
       </c>
       <c r="R46" t="n">
-        <v>7056149</v>
+        <v>7055225</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5449,12 +5363,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5481,10 +5395,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127456634</v>
+        <v>89594505</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>81236</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5492,34 +5411,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463385</v>
+        <v>463521.9401843805</v>
       </c>
       <c r="R47" t="n">
-        <v>7055637</v>
+        <v>7055844.888383466</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5546,17 +5465,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5565,63 +5489,73 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127456627</v>
+        <v>89594508</v>
       </c>
       <c r="B48" t="n">
-        <v>91348</v>
+        <v>5135</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463538</v>
+        <v>463507.9449135439</v>
       </c>
       <c r="R48" t="n">
-        <v>7055899</v>
+        <v>7055828.152650622</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5648,12 +5582,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,19 +5608,2300 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>89594529</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5113</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>463422.1366394605</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7055838.924257813</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127456608</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>463435</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7055686</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127456628</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>463461</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7055899</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127456629</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>463485</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7055874</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127456633</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>463600</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7056150</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127456623</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>463387</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7055632</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127456632</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>463475</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7056315</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127456606</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>463477</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7055687</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127456605</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>463648</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7056396</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127456624</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57494</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>463434</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7056142</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127456607</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>463448</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7055699</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127456635</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>463389</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7055462</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127456626</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57765</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>463436</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7056149</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127456634</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>463385</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7055637</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127456627</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>463538</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7055899</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127690767</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>463403</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7056139</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127690745</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>463424</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7055709</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127690758</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>463576</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7056001</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127690747</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>463380</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7055364</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127690744</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>463409</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7055695</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127690762</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>463451</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7056320</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ganska färska Hack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127690757</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tjockmjölkbodshön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>463682</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7056359</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -3976,7 +3976,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127690748</v>
+        <v>127690750</v>
       </c>
       <c r="B33" t="n">
         <v>57661</v>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463192</v>
+        <v>463270</v>
       </c>
       <c r="R33" t="n">
-        <v>7055213</v>
+        <v>7055207</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127690750</v>
+        <v>127690748</v>
       </c>
       <c r="B34" t="n">
         <v>57661</v>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463270</v>
+        <v>463192</v>
       </c>
       <c r="R34" t="n">
-        <v>7055207</v>
+        <v>7055213</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127690754</v>
+        <v>127690753</v>
       </c>
       <c r="B35" t="n">
         <v>57661</v>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463174</v>
+        <v>463141</v>
       </c>
       <c r="R35" t="n">
-        <v>7054944</v>
+        <v>7054981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127690753</v>
+        <v>127690754</v>
       </c>
       <c r="B36" t="n">
         <v>57661</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463141</v>
+        <v>463174</v>
       </c>
       <c r="R36" t="n">
-        <v>7054981</v>
+        <v>7054944</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127690743</v>
+        <v>127690756</v>
       </c>
       <c r="B42" t="n">
         <v>57661</v>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463122</v>
+        <v>463174</v>
       </c>
       <c r="R42" t="n">
-        <v>7054927</v>
+        <v>7054942</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127690756</v>
+        <v>127690743</v>
       </c>
       <c r="B43" t="n">
         <v>57661</v>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463174</v>
+        <v>463122</v>
       </c>
       <c r="R43" t="n">
-        <v>7054942</v>
+        <v>7054927</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B59" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R59" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R60" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6884,61 +6884,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B61" t="n">
-        <v>57765</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R61" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6971,6 +6955,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6997,45 +6986,61 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>57765</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R62" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7068,11 +7073,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6884,45 +6884,61 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>57765</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R61" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6955,11 +6971,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6986,61 +6997,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B62" t="n">
-        <v>57765</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R62" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7073,6 +7068,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>127456613</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127456602</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127456612</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127456611</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127456637</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127456609</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127456631</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127456614</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127456610</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127456600</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>127456604</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127456601</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127456625</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127456636</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>127690750</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>127690748</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127690753</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127690754</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B38" t="n">
-        <v>91326</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R38" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,6 +4552,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4583,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>91328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4589,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R39" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4649,11 +4654,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4683,7 +4683,7 @@
         <v>127690749</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>127690763</v>
       </c>
       <c r="B41" t="n">
-        <v>57572</v>
+        <v>57574</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127690756</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>127690743</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>127690751</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>127456608</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>127456633</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>127456623</v>
       </c>
       <c r="B54" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>127456632</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B56" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R56" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B57" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R57" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>57496</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R59" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B60" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R60" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6884,61 +6884,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B61" t="n">
-        <v>57765</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R61" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6971,6 +6955,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6997,45 +6986,61 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>57767</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R62" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7068,11 +7073,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>127690745</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>127690758</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>127690747</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>127690744</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>127690762</v>
       </c>
       <c r="B69" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127690757</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R19" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,11 +2654,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,21 +2691,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R20" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,6 +2751,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>91328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R38" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,11 +4552,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4583,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>91328</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,21 +4589,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R39" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,6 +4649,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6367,7 +6367,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B56" t="n">
         <v>57663</v>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R56" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B57" t="n">
         <v>57663</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R57" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6884,45 +6884,61 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>57767</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R61" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6955,11 +6971,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6986,61 +6997,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B62" t="n">
-        <v>57767</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R62" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7073,6 +7068,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R19" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,6 +2654,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,21 +2696,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R20" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,11 +2756,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -6367,7 +6367,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B56" t="n">
         <v>57663</v>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R56" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B57" t="n">
         <v>57663</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R57" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B59" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R59" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R60" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R19" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,11 +2654,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,21 +2691,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R20" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,6 +2751,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6884,61 +6884,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456626</v>
+        <v>127456634</v>
       </c>
       <c r="B61" t="n">
-        <v>57767</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463436</v>
+        <v>463385</v>
       </c>
       <c r="R61" t="n">
-        <v>7056149</v>
+        <v>7055637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6971,6 +6955,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6997,45 +6986,61 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>57767</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R62" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7068,11 +7073,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>127456613</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127456602</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127456612</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127456611</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127456637</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127456614</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127456610</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127456600</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>127456604</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127456601</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127456625</v>
       </c>
       <c r="B29" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127456636</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>127690750</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>127690748</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127690753</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127690754</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>127690749</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>127690763</v>
       </c>
       <c r="B41" t="n">
-        <v>57574</v>
+        <v>57577</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127690756</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>127690743</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>127690751</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>127456608</v>
       </c>
       <c r="B50" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>127456633</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>127456623</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>127456632</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127456605</v>
       </c>
       <c r="B56" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127456606</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57496</v>
+        <v>57499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>127456635</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>127456607</v>
       </c>
       <c r="B60" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>127456634</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>127456626</v>
       </c>
       <c r="B62" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>127690745</v>
       </c>
       <c r="B65" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>127690758</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>127690747</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>127690744</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>127690762</v>
       </c>
       <c r="B69" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127690757</v>
       </c>
       <c r="B70" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>127456613</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127456602</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127456612</v>
+        <v>127456611</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463233</v>
+        <v>463253</v>
       </c>
       <c r="R16" t="n">
-        <v>7054875</v>
+        <v>7054891</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127456611</v>
+        <v>127456612</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463253</v>
+        <v>463233</v>
       </c>
       <c r="R17" t="n">
-        <v>7054891</v>
+        <v>7054875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,7 +2484,7 @@
         <v>127456637</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127456614</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>127456610</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127456600</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>127456604</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127456601</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>127456625</v>
       </c>
       <c r="B29" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127456636</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>127690750</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>127690748</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127690753</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127690754</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B38" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R38" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,6 +4552,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4583,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4589,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R39" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4649,11 +4654,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4683,7 +4683,7 @@
         <v>127690749</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>127690763</v>
       </c>
       <c r="B41" t="n">
-        <v>57577</v>
+        <v>57583</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127690756</v>
+        <v>127690743</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463174</v>
+        <v>463122</v>
       </c>
       <c r="R42" t="n">
-        <v>7054942</v>
+        <v>7054927</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,10 +4997,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127690743</v>
+        <v>127690756</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463122</v>
+        <v>463174</v>
       </c>
       <c r="R43" t="n">
-        <v>7054927</v>
+        <v>7054942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>127690751</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>127456608</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>127456633</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>127456623</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>127456632</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R56" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R57" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57499</v>
+        <v>57505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>127456635</v>
       </c>
       <c r="B59" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>127456607</v>
       </c>
       <c r="B60" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>127456634</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>127456626</v>
       </c>
       <c r="B62" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>127690745</v>
       </c>
       <c r="B65" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>127690758</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>127690747</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>127690744</v>
       </c>
       <c r="B68" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>127690762</v>
       </c>
       <c r="B69" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127690757</v>
       </c>
       <c r="B70" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127456611</v>
+        <v>127456612</v>
       </c>
       <c r="B16" t="n">
         <v>57672</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463253</v>
+        <v>463233</v>
       </c>
       <c r="R16" t="n">
-        <v>7054891</v>
+        <v>7054875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127456612</v>
+        <v>127456611</v>
       </c>
       <c r="B17" t="n">
         <v>57672</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463233</v>
+        <v>463253</v>
       </c>
       <c r="R17" t="n">
-        <v>7054875</v>
+        <v>7054891</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B19" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R19" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,6 +2654,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,21 +2696,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R20" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,11 +2756,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127690753</v>
+        <v>127690754</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463141</v>
+        <v>463174</v>
       </c>
       <c r="R35" t="n">
-        <v>7054981</v>
+        <v>7054944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127690754</v>
+        <v>127690753</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463174</v>
+        <v>463141</v>
       </c>
       <c r="R36" t="n">
-        <v>7054944</v>
+        <v>7054981</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R38" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,11 +4552,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4583,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,21 +4589,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R39" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,6 +4649,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456606</v>
+        <v>127456605</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463477</v>
+        <v>463648</v>
       </c>
       <c r="R56" t="n">
-        <v>7055687</v>
+        <v>7056396</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456605</v>
+        <v>127456606</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463648</v>
+        <v>463477</v>
       </c>
       <c r="R57" t="n">
-        <v>7056396</v>
+        <v>7055687</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127690747</v>
+        <v>127690744</v>
       </c>
       <c r="B67" t="n">
         <v>57672</v>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463380</v>
+        <v>463409</v>
       </c>
       <c r="R67" t="n">
-        <v>7055364</v>
+        <v>7055695</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7599,7 +7599,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127690744</v>
+        <v>127690747</v>
       </c>
       <c r="B68" t="n">
         <v>57672</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>463409</v>
+        <v>463380</v>
       </c>
       <c r="R68" t="n">
-        <v>7055695</v>
+        <v>7055364</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456609</v>
+        <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463323</v>
+        <v>463258</v>
       </c>
       <c r="R19" t="n">
-        <v>7055206</v>
+        <v>7054968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,11 +2654,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456631</v>
+        <v>127456609</v>
       </c>
       <c r="B20" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,21 +2691,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463258</v>
+        <v>463323</v>
       </c>
       <c r="R20" t="n">
-        <v>7054968</v>
+        <v>7055206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,6 +2751,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127690743</v>
+        <v>127690756</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463122</v>
+        <v>463174</v>
       </c>
       <c r="R42" t="n">
-        <v>7054927</v>
+        <v>7054942</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127690756</v>
+        <v>127690743</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463174</v>
+        <v>463122</v>
       </c>
       <c r="R43" t="n">
-        <v>7054942</v>
+        <v>7054927</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R59" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R60" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7497,7 +7497,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127690744</v>
+        <v>127690747</v>
       </c>
       <c r="B67" t="n">
         <v>57672</v>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>463409</v>
+        <v>463380</v>
       </c>
       <c r="R67" t="n">
-        <v>7055695</v>
+        <v>7055364</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7599,7 +7599,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127690747</v>
+        <v>127690744</v>
       </c>
       <c r="B68" t="n">
         <v>57672</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>463380</v>
+        <v>463409</v>
       </c>
       <c r="R68" t="n">
-        <v>7055364</v>
+        <v>7055695</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127690769</v>
+        <v>127690750</v>
       </c>
       <c r="B32" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463244</v>
+        <v>463270</v>
       </c>
       <c r="R32" t="n">
-        <v>7055263</v>
+        <v>7055207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,6 +3950,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3976,7 +3981,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127690750</v>
+        <v>127690748</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4011,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463270</v>
+        <v>463192</v>
       </c>
       <c r="R33" t="n">
-        <v>7055207</v>
+        <v>7055213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,10 +4083,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127690748</v>
+        <v>127690769</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4089,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4113,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463192</v>
+        <v>463244</v>
       </c>
       <c r="R34" t="n">
-        <v>7055213</v>
+        <v>7055263</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,11 +4154,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127690754</v>
+        <v>127690753</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463174</v>
+        <v>463141</v>
       </c>
       <c r="R35" t="n">
-        <v>7054944</v>
+        <v>7054981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127690753</v>
+        <v>127690754</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463141</v>
+        <v>463174</v>
       </c>
       <c r="R36" t="n">
-        <v>7054981</v>
+        <v>7054944</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R59" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R60" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>127456631</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127456630</v>
       </c>
       <c r="B21" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127456639</v>
       </c>
       <c r="B24" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>127456638</v>
       </c>
       <c r="B28" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127456640</v>
       </c>
       <c r="B30" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127690750</v>
+        <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463270</v>
+        <v>463244</v>
       </c>
       <c r="R32" t="n">
-        <v>7055207</v>
+        <v>7055263</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,11 +3950,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,7 +3976,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127690748</v>
+        <v>127690750</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -4016,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463192</v>
+        <v>463270</v>
       </c>
       <c r="R33" t="n">
-        <v>7055213</v>
+        <v>7055207</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127690769</v>
+        <v>127690748</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4094,21 +4089,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463244</v>
+        <v>463192</v>
       </c>
       <c r="R34" t="n">
-        <v>7055263</v>
+        <v>7055213</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,6 +4149,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B38" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R38" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,6 +4552,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4583,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4589,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R39" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4649,11 +4654,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127456628</v>
       </c>
       <c r="B51" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127456629</v>
       </c>
       <c r="B52" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>127456627</v>
       </c>
       <c r="B63" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -4481,10 +4481,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690752</v>
+        <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463101</v>
+        <v>463254</v>
       </c>
       <c r="R38" t="n">
-        <v>7054992</v>
+        <v>7055069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,11 +4552,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4583,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690765</v>
+        <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,21 +4589,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463254</v>
+        <v>463101</v>
       </c>
       <c r="R39" t="n">
-        <v>7055069</v>
+        <v>7054992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,6 +4649,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6680,10 +6680,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456635</v>
+        <v>127456607</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6691,21 +6691,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463389</v>
+        <v>463448</v>
       </c>
       <c r="R59" t="n">
-        <v>7055462</v>
+        <v>7055699</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6782,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456607</v>
+        <v>127456635</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,21 +6793,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463448</v>
+        <v>463389</v>
       </c>
       <c r="R60" t="n">
-        <v>7055699</v>
+        <v>7055462</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -3882,7 +3882,7 @@
         <v>127690769</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>127690750</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>127690748</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>127690753</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127690754</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127690768</v>
       </c>
       <c r="B37" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>127690765</v>
       </c>
       <c r="B38" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>127690752</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>127690749</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>127690763</v>
       </c>
       <c r="B41" t="n">
-        <v>57583</v>
+        <v>57584</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127690756</v>
+        <v>127690743</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463174</v>
+        <v>463122</v>
       </c>
       <c r="R42" t="n">
-        <v>7054942</v>
+        <v>7054927</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,10 +4997,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127690743</v>
+        <v>127690756</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463122</v>
+        <v>463174</v>
       </c>
       <c r="R43" t="n">
-        <v>7054927</v>
+        <v>7054942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,7 +5102,7 @@
         <v>127690766</v>
       </c>
       <c r="B44" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>127690751</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>127690764</v>
       </c>
       <c r="B46" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>127690767</v>
       </c>
       <c r="B64" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>127690745</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>127690758</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>127690747</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>127690744</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>127690762</v>
       </c>
       <c r="B69" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127690757</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -3879,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127690769</v>
+        <v>127690750</v>
       </c>
       <c r="B32" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463244</v>
+        <v>463270</v>
       </c>
       <c r="R32" t="n">
-        <v>7055263</v>
+        <v>7055207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,6 +3950,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3976,7 +3981,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127690750</v>
+        <v>127690748</v>
       </c>
       <c r="B33" t="n">
         <v>57673</v>
@@ -4011,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463270</v>
+        <v>463192</v>
       </c>
       <c r="R33" t="n">
-        <v>7055207</v>
+        <v>7055213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,10 +4083,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127690748</v>
+        <v>127690769</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4089,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4113,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463192</v>
+        <v>463244</v>
       </c>
       <c r="R34" t="n">
-        <v>7055213</v>
+        <v>7055263</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,11 +4154,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57505</v>
+        <v>57517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57517</v>
+        <v>57521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57521</v>
+        <v>57548</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57548</v>
+        <v>57552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -6574,7 +6574,7 @@
         <v>127456624</v>
       </c>
       <c r="B58" t="n">
-        <v>57552</v>
+        <v>57555</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89594560</v>
+        <v>89594537</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463203.79435653</v>
+        <v>463127</v>
       </c>
       <c r="R2" t="n">
-        <v>7055363.857079709</v>
+        <v>7055003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -794,16 +784,11 @@
         <v>89594558</v>
       </c>
       <c r="B3" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463335.0756597399</v>
+        <v>463335</v>
       </c>
       <c r="R3" t="n">
-        <v>7055856.82709547</v>
+        <v>7055857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +849,9 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89594546</v>
+        <v>127456638</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463223.0043220884</v>
+        <v>463269</v>
       </c>
       <c r="R4" t="n">
-        <v>7054946.903068512</v>
+        <v>7055595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,66 +967,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89594543</v>
+        <v>127456639</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463201.9101043284</v>
+        <v>463369</v>
       </c>
       <c r="R5" t="n">
-        <v>7055354.984516118</v>
+        <v>7055407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,31 +1064,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89594537</v>
+        <v>127456640</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,34 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463127.0131604018</v>
+        <v>463328</v>
       </c>
       <c r="R6" t="n">
-        <v>7055003.170262886</v>
+        <v>7055209</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,22 +1141,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,75 +1157,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89594516</v>
+        <v>127690764</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463192.8862677459</v>
+        <v>463175</v>
       </c>
       <c r="R7" t="n">
-        <v>7055344.86065209</v>
+        <v>7055225</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,22 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,31 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89594551</v>
+        <v>127690765</v>
       </c>
       <c r="B8" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,34 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1841</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463164.786147472</v>
+        <v>463254</v>
       </c>
       <c r="R8" t="n">
-        <v>7055225.998804032</v>
+        <v>7055069</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,22 +1335,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,31 +1355,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89594498</v>
+        <v>127690766</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,34 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463269.0981019526</v>
+        <v>463238</v>
       </c>
       <c r="R9" t="n">
-        <v>7054965.938929494</v>
+        <v>7055089</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,22 +1432,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,35 +1452,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89594534</v>
+        <v>89594492</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1644,14 +1495,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Erik-Erstjärnarna, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463238.0412516395</v>
+        <v>463271</v>
       </c>
       <c r="R10" t="n">
-        <v>7055168.221126091</v>
+        <v>7055815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,19 +1532,9 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,37 +1565,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89594528</v>
+        <v>89594534</v>
       </c>
       <c r="B11" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1764,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463201.9101043284</v>
+        <v>463238</v>
       </c>
       <c r="R11" t="n">
-        <v>7055354.984516118</v>
+        <v>7055168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,19 +1633,9 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,37 +1666,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89594552</v>
+        <v>89594516</v>
       </c>
       <c r="B12" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463205.0526905976</v>
+        <v>463193</v>
       </c>
       <c r="R12" t="n">
-        <v>7055357.171647201</v>
+        <v>7055345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,28 +1734,17 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1957,15 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89594527</v>
+        <v>89594546</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1997,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463206.8543509306</v>
+        <v>463223</v>
       </c>
       <c r="R13" t="n">
-        <v>7055358.929622275</v>
+        <v>7054947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,19 +1835,9 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127456613</v>
+        <v>89594505</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,34 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463188</v>
+        <v>463522</v>
       </c>
       <c r="R14" t="n">
-        <v>7054869</v>
+        <v>7055845</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,17 +1933,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,28 +1947,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127456602</v>
+        <v>89594551</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>97453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,34 +1981,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463073</v>
+        <v>463165</v>
       </c>
       <c r="R15" t="n">
-        <v>7055011</v>
+        <v>7055226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,17 +2035,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,22 +2055,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127456612</v>
+        <v>89594527</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,34 +2082,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463233</v>
+        <v>463207</v>
       </c>
       <c r="R16" t="n">
-        <v>7054875</v>
+        <v>7055359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,17 +2136,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,44 +2156,48 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127456611</v>
+        <v>127456632</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463253</v>
+        <v>463475</v>
       </c>
       <c r="R17" t="n">
-        <v>7054891</v>
+        <v>7056315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,14 +2274,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127456637</v>
+        <v>127456633</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2516,10 +2309,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463218</v>
+        <v>463600</v>
       </c>
       <c r="R18" t="n">
-        <v>7054785</v>
+        <v>7056150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,32 +2376,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127456631</v>
+        <v>127456634</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463258</v>
+        <v>463385</v>
       </c>
       <c r="R19" t="n">
-        <v>7054968</v>
+        <v>7055637</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,6 +2447,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,32 +2478,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127456609</v>
+        <v>127456635</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2715,10 +2513,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463323</v>
+        <v>463389</v>
       </c>
       <c r="R20" t="n">
-        <v>7055206</v>
+        <v>7055462</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2755,7 +2553,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2782,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127456630</v>
+        <v>127456636</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2817,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463334</v>
+        <v>463274</v>
       </c>
       <c r="R21" t="n">
-        <v>7055224</v>
+        <v>7055044</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,6 +2651,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,32 +2682,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127456614</v>
+        <v>127456637</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2914,10 +2717,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463186</v>
+        <v>463218</v>
       </c>
       <c r="R22" t="n">
-        <v>7054865</v>
+        <v>7054785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,7 +2757,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2981,45 +2784,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127456610</v>
+        <v>89594552</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>75300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463220</v>
+        <v>463205</v>
       </c>
       <c r="R23" t="n">
-        <v>7054981</v>
+        <v>7055357</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3046,47 +2849,47 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127456639</v>
+        <v>89594560</v>
       </c>
       <c r="B24" t="n">
-        <v>88755</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,34 +2897,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463369</v>
+        <v>463204</v>
       </c>
       <c r="R24" t="n">
-        <v>7055407</v>
+        <v>7055364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3148,12 +2951,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,22 +2971,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127456600</v>
+        <v>127456625</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +2998,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3022,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463051</v>
+        <v>463207</v>
       </c>
       <c r="R25" t="n">
-        <v>7054759</v>
+        <v>7055365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,11 +3058,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,45 +3084,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127456604</v>
+        <v>89594543</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463298</v>
+        <v>463202</v>
       </c>
       <c r="R26" t="n">
-        <v>7055633</v>
+        <v>7055355</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3347,17 +3149,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3372,57 +3169,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127456601</v>
+        <v>89594528</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Erik-Erstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463062</v>
+        <v>463202</v>
       </c>
       <c r="R27" t="n">
-        <v>7054993</v>
+        <v>7055355</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,17 +3250,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,22 +3270,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127456638</v>
+        <v>127690763</v>
       </c>
       <c r="B28" t="n">
-        <v>88755</v>
+        <v>57864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,34 +3297,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100011</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463269</v>
+        <v>463125</v>
       </c>
       <c r="R28" t="n">
-        <v>7055595</v>
+        <v>7054733</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,12 +3367,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,32 +3399,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127456625</v>
+        <v>127690762</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3618,10 +3434,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463207</v>
+        <v>463451</v>
       </c>
       <c r="R29" t="n">
-        <v>7055365</v>
+        <v>7056320</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,12 +3464,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ganska färska Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,10 +3501,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127456640</v>
+        <v>127456600</v>
       </c>
       <c r="B30" t="n">
-        <v>88755</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,21 +3512,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463328</v>
+        <v>463051</v>
       </c>
       <c r="R30" t="n">
-        <v>7055209</v>
+        <v>7054759</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,6 +3572,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,10 +3603,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127456636</v>
+        <v>127456601</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,21 +3614,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3638,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463274</v>
+        <v>463062</v>
       </c>
       <c r="R31" t="n">
-        <v>7055044</v>
+        <v>7054993</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,7 +3678,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3879,10 +3705,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127690750</v>
+        <v>127456602</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463270</v>
+        <v>463073</v>
       </c>
       <c r="R32" t="n">
-        <v>7055207</v>
+        <v>7055011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,17 +3770,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127690748</v>
+        <v>127456604</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4016,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463192</v>
+        <v>463298</v>
       </c>
       <c r="R33" t="n">
-        <v>7055213</v>
+        <v>7055633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,17 +3872,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4083,10 +3909,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127690769</v>
+        <v>127456605</v>
       </c>
       <c r="B34" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4094,21 +3920,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +3944,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463244</v>
+        <v>463648</v>
       </c>
       <c r="R34" t="n">
-        <v>7055263</v>
+        <v>7056396</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4148,12 +3974,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4180,10 +4011,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127690753</v>
+        <v>127456606</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,10 +4046,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463141</v>
+        <v>463477</v>
       </c>
       <c r="R35" t="n">
-        <v>7054981</v>
+        <v>7055687</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4245,12 +4076,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4282,10 +4113,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127690754</v>
+        <v>127456607</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4317,10 +4148,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463174</v>
+        <v>463448</v>
       </c>
       <c r="R36" t="n">
-        <v>7054944</v>
+        <v>7055699</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4347,17 +4178,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4384,10 +4215,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127690768</v>
+        <v>127456608</v>
       </c>
       <c r="B37" t="n">
-        <v>91378</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,21 +4226,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4419,10 +4250,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463242</v>
+        <v>463435</v>
       </c>
       <c r="R37" t="n">
-        <v>7055254</v>
+        <v>7055686</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,12 +4280,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4481,10 +4317,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127690765</v>
+        <v>127456609</v>
       </c>
       <c r="B38" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,21 +4328,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463254</v>
+        <v>463323</v>
       </c>
       <c r="R38" t="n">
-        <v>7055069</v>
+        <v>7055206</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,12 +4382,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127690752</v>
+        <v>127456610</v>
       </c>
       <c r="B39" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4613,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463101</v>
+        <v>463220</v>
       </c>
       <c r="R39" t="n">
-        <v>7054992</v>
+        <v>7054981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4643,17 +4484,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4680,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127690749</v>
+        <v>127456611</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463268</v>
+        <v>463253</v>
       </c>
       <c r="R40" t="n">
-        <v>7055199</v>
+        <v>7054891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4745,17 +4586,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4782,10 +4623,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127690763</v>
+        <v>127456612</v>
       </c>
       <c r="B41" t="n">
-        <v>57584</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4793,16 +4634,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100011</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4810,33 +4651,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463125</v>
+        <v>463233</v>
       </c>
       <c r="R41" t="n">
-        <v>7054733</v>
+        <v>7054875</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4863,12 +4688,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,10 +4725,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127690743</v>
+        <v>127456613</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4930,10 +4760,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463122</v>
+        <v>463188</v>
       </c>
       <c r="R42" t="n">
-        <v>7054927</v>
+        <v>7054869</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4960,17 +4790,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4997,10 +4827,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127690756</v>
+        <v>127456614</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,10 +4862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463174</v>
+        <v>463186</v>
       </c>
       <c r="R43" t="n">
-        <v>7054942</v>
+        <v>7054865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5062,17 +4892,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,10 +4929,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127690766</v>
+        <v>127690743</v>
       </c>
       <c r="B44" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5110,21 +4940,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5134,10 +4964,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463238</v>
+        <v>463122</v>
       </c>
       <c r="R44" t="n">
-        <v>7055089</v>
+        <v>7054927</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5170,6 +5000,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5196,10 +5031,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127690751</v>
+        <v>127690744</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,10 +5066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463252</v>
+        <v>463409</v>
       </c>
       <c r="R45" t="n">
-        <v>7055162</v>
+        <v>7055695</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,7 +5106,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5298,10 +5133,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127690764</v>
+        <v>127690745</v>
       </c>
       <c r="B46" t="n">
-        <v>91356</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5309,21 +5144,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5168,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>463175</v>
+        <v>463424</v>
       </c>
       <c r="R46" t="n">
-        <v>7055225</v>
+        <v>7055709</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5369,6 +5204,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5395,15 +5235,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>89594505</v>
+        <v>127690747</v>
       </c>
       <c r="B47" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,34 +5246,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463521.9401843805</v>
+        <v>463380</v>
       </c>
       <c r="R47" t="n">
-        <v>7055844.888383466</v>
+        <v>7055364</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5465,22 +5300,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5489,55 +5319,45 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>89594508</v>
+        <v>127690748</v>
       </c>
       <c r="B48" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5548,14 +5368,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463507.9449135439</v>
+        <v>463192</v>
       </c>
       <c r="R48" t="n">
-        <v>7055828.152650622</v>
+        <v>7055213</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5582,22 +5402,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5608,75 +5423,61 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>89594529</v>
+        <v>127690749</v>
       </c>
       <c r="B49" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodhön, Jmt</t>
+          <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>463422.1366394605</v>
+        <v>463268</v>
       </c>
       <c r="R49" t="n">
-        <v>7055838.924257813</v>
+        <v>7055199</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5703,22 +5504,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5729,35 +5525,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127456608</v>
+        <v>127690750</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,10 +5576,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>463435</v>
+        <v>463270</v>
       </c>
       <c r="R50" t="n">
-        <v>7055686</v>
+        <v>7055207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5819,17 +5606,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,10 +5643,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127456628</v>
+        <v>127690751</v>
       </c>
       <c r="B51" t="n">
-        <v>91370</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5867,21 +5654,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5891,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463461</v>
+        <v>463252</v>
       </c>
       <c r="R51" t="n">
-        <v>7055899</v>
+        <v>7055162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5921,12 +5708,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5953,10 +5745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127456629</v>
+        <v>127690752</v>
       </c>
       <c r="B52" t="n">
-        <v>91370</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5964,21 +5756,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5988,10 +5780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463485</v>
+        <v>463101</v>
       </c>
       <c r="R52" t="n">
-        <v>7055874</v>
+        <v>7054992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6018,12 +5810,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6050,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127456633</v>
+        <v>127690753</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6061,21 +5858,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6085,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>463600</v>
+        <v>463141</v>
       </c>
       <c r="R53" t="n">
-        <v>7056150</v>
+        <v>7054981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6115,17 +5912,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6152,10 +5949,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127456623</v>
+        <v>127690754</v>
       </c>
       <c r="B54" t="n">
-        <v>57832</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6163,50 +5960,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463387</v>
+        <v>463174</v>
       </c>
       <c r="R54" t="n">
-        <v>7055632</v>
+        <v>7054944</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6233,12 +6014,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6265,10 +6051,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127456632</v>
+        <v>127690756</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6276,21 +6062,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6300,10 +6086,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463475</v>
+        <v>463174</v>
       </c>
       <c r="R55" t="n">
-        <v>7056315</v>
+        <v>7054942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6330,17 +6116,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6367,10 +6153,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127456605</v>
+        <v>127690757</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6402,10 +6188,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463648</v>
+        <v>463682</v>
       </c>
       <c r="R56" t="n">
-        <v>7056396</v>
+        <v>7056359</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6432,17 +6218,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,10 +6255,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127456606</v>
+        <v>127690758</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6504,10 +6290,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463477</v>
+        <v>463576</v>
       </c>
       <c r="R57" t="n">
-        <v>7055687</v>
+        <v>7056001</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6534,17 +6320,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6571,10 +6357,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127456624</v>
+        <v>89594529</v>
       </c>
       <c r="B58" t="n">
-        <v>57555</v>
+        <v>5179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6582,46 +6368,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102622</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>463434</v>
+        <v>463422</v>
       </c>
       <c r="R58" t="n">
-        <v>7056142</v>
+        <v>7055839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6648,12 +6422,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6664,43 +6438,52 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127456607</v>
+        <v>127456624</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>57785</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>102622</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6708,17 +6491,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463448</v>
+        <v>463434</v>
       </c>
       <c r="R59" t="n">
-        <v>7055699</v>
+        <v>7056142</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6751,11 +6546,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6782,10 +6572,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127456635</v>
+        <v>127456623</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6793,34 +6583,50 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>463389</v>
+        <v>463387</v>
       </c>
       <c r="R60" t="n">
-        <v>7055462</v>
+        <v>7055632</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6853,11 +6659,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6884,10 +6685,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127456634</v>
+        <v>127456626</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6895,34 +6696,50 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tjockmjölkbodshön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463385</v>
+        <v>463436</v>
       </c>
       <c r="R61" t="n">
-        <v>7055637</v>
+        <v>7056149</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6955,11 +6772,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6986,10 +6798,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127456626</v>
+        <v>89594508</v>
       </c>
       <c r="B62" t="n">
-        <v>57776</v>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6997,16 +6809,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7014,33 +6826,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
+          <t>Tjockmjölkbodhön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>463436</v>
+        <v>463508</v>
       </c>
       <c r="R62" t="n">
-        <v>7056149</v>
+        <v>7055828</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7067,12 +6863,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7083,825 +6879,28 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>127456627</v>
-      </c>
-      <c r="B63" t="n">
-        <v>91370</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>463538</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7055899</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>127690767</v>
-      </c>
-      <c r="B64" t="n">
-        <v>91378</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>463403</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7056139</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>127690745</v>
-      </c>
-      <c r="B65" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>463424</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7055709</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>127690758</v>
-      </c>
-      <c r="B66" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>463576</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7056001</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>127690747</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>463380</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7055364</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>127690744</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>463409</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7055695</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>127690762</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57670</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>463451</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7056320</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ganska färska Hack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>127690757</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Tjockmjölkbodshön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>463682</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7056359</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34013-2025 artfynd.xlsx
+++ b/artfynd/A 34013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594537</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456640</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690765</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594534</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594516</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594546</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1967,6 +2032,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594505</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594551</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594527</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2271,6 +2351,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456632</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456633</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456634</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2577,6 +2672,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456635</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2679,6 +2779,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456636</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456637</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594552</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594560</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3081,6 +3201,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456625</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3182,6 +3307,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594543</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3283,6 +3413,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594528</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3396,6 +3531,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690763</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3498,6 +3638,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690762</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3600,6 +3745,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456600</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456601</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3804,6 +3959,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456602</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456604</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456605</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4110,6 +4280,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456606</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456607</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4314,6 +4494,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456608</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4416,6 +4601,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456609</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4518,6 +4708,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456610</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4620,6 +4815,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456611</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4722,6 +4922,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4824,6 +5029,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456613</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4926,6 +5136,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456614</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5028,6 +5243,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690743</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5130,6 +5350,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690744</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5232,6 +5457,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690745</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5334,6 +5564,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690747</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5436,6 +5671,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690748</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5538,6 +5778,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690749</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5640,6 +5885,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690750</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5742,6 +5992,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690751</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5844,6 +6099,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690752</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5946,6 +6206,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690753</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6048,6 +6313,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690754</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6150,6 +6420,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690756</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6252,6 +6527,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690757</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6354,6 +6634,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127690758</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6460,6 +6745,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594529</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6569,6 +6859,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456624</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6682,6 +6977,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456623</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6795,6 +7095,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456626</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6901,8 +7206,76 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>